--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01D0356-386C-443D-8B96-6C4D1E8D26B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C8AE80-0C0D-4343-BF98-64F518D55BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5910" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5937" uniqueCount="1341">
   <si>
     <t>Name</t>
   </si>
@@ -4042,6 +4042,12 @@
   </si>
   <si>
     <t>0498</t>
+  </si>
+  <si>
+    <t>0428</t>
+  </si>
+  <si>
+    <t>SHITU</t>
   </si>
 </sst>
 </file>
@@ -17924,7 +17930,7 @@
         <v>35</v>
       </c>
       <c r="C1233">
-        <v>9591</v>
+        <v>9551</v>
       </c>
     </row>
     <row r="1234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22192,7 +22198,7 @@
         <v>35</v>
       </c>
       <c r="C1621">
-        <v>1726</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -31320,9 +31326,6 @@
       <c r="B2452" t="s">
         <v>44</v>
       </c>
-      <c r="C2452">
-        <v>4570</v>
-      </c>
     </row>
     <row r="2453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2453" t="s">
@@ -31652,6 +31655,149 @@
       </c>
       <c r="C2482">
         <v>1218</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2483" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B2483" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2483" s="4" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2484" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B2484" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2484">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2485" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B2485" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2485" s="4">
+        <v>8575</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2486" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B2486" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2486">
+        <v>9815</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2487" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B2487" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2487" s="4">
+        <v>5431</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2488" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B2488" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2488">
+        <v>6093</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2489" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2489" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2489" s="4">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2490" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2490" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2490">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2491" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2491" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2491" s="4">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2492" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2492" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2492">
+        <v>5294</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2493" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2493" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2493" s="4">
+        <v>3842</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2494" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2494" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2494">
+        <v>9583</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2495" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2495" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2495" s="4">
+        <v>9779</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C8AE80-0C0D-4343-BF98-64F518D55BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE58032-38C7-4590-8576-CDD4710EF5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5937" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5949" uniqueCount="1343">
   <si>
     <t>Name</t>
   </si>
@@ -4048,6 +4048,12 @@
   </si>
   <si>
     <t>SHITU</t>
+  </si>
+  <si>
+    <t>malkeet rinku</t>
+  </si>
+  <si>
+    <t>0248</t>
   </si>
 </sst>
 </file>
@@ -29770,7 +29776,7 @@
     </row>
     <row r="2310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2310" t="s">
-        <v>1306</v>
+        <v>1068</v>
       </c>
       <c r="B2310" s="6" t="s">
         <v>52</v>
@@ -31798,6 +31804,61 @@
       </c>
       <c r="C2495" s="4">
         <v>9779</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2496" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2496" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2496">
+        <v>8435</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2497" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2497" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2497" s="4">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2498" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2498" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2498" s="4" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2499" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2499" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2499" s="4" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2500" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2500" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2500" s="4">
+        <v>2258</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE58032-38C7-4590-8576-CDD4710EF5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B104CD59-80B0-4DA2-9F07-4D41607A647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5949" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5988" uniqueCount="1346">
   <si>
     <t>Name</t>
   </si>
@@ -4054,6 +4054,15 @@
   </si>
   <si>
     <t>0248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aman </t>
+  </si>
+  <si>
+    <t>UCB0002347</t>
+  </si>
+  <si>
+    <t>2857</t>
   </si>
 </sst>
 </file>
@@ -31861,6 +31870,215 @@
         <v>2258</v>
       </c>
     </row>
+    <row r="2501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2501" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2501" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2501" s="4">
+        <v>7578</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2502" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2502" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C2502" s="4">
+        <v>5237</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2503" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2503" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C2503" s="4">
+        <v>3671</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2504" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2504" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2504" s="4">
+        <v>8435</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2505" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2505" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2505" s="4">
+        <v>5969</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2506" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2506" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2506" s="4">
+        <v>9310</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2507" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2507" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2507" s="4">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2508" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2508" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2508" s="4">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2509" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2509" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2509" s="4">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2510" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2510" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2510" s="4">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2511" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2511" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2511" s="4">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2512" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2512" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2512" s="4">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2513" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2513" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2513" s="4">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2514" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2514" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2514" s="4">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2515" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2515" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2515" s="4">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2516" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2516" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2516" s="4">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2517" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2517" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2517" s="4">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2518" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2518" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2518" s="4">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2519" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2519" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2519" s="4" t="s">
+        <v>1345</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B104CD59-80B0-4DA2-9F07-4D41607A647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5916D7-E0C3-4743-B0A2-EFB3CE2FA9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5988" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6048" uniqueCount="1349">
   <si>
     <t>Name</t>
   </si>
@@ -4063,6 +4063,15 @@
   </si>
   <si>
     <t>2857</t>
+  </si>
+  <si>
+    <t>7811</t>
+  </si>
+  <si>
+    <t>0678</t>
+  </si>
+  <si>
+    <t>0112</t>
   </si>
 </sst>
 </file>
@@ -32079,6 +32088,314 @@
         <v>1345</v>
       </c>
     </row>
+    <row r="2520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2520" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2520" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2520" s="4" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2521" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2521" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2521" s="4">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2522" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2522" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2522" s="4">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2523" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2523" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2523" s="4">
+        <v>9818</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2524" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2524" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2524" s="4">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2525" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2525" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2525" s="4">
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2526" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2526" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2526" s="4">
+        <v>6815</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2527" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2527" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2527" s="4">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2528" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2528" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2528" s="4" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2529" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2529" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2529" s="4">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2530" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2530" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2530" s="4" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2531" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2531" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2531" s="4">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2532" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2532" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2532" s="4">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2533" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2533" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2533" s="4">
+        <v>6541</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2534" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2534" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2534" s="4">
+        <v>8384</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2535" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2535" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2535" s="4">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2536" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2536" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2536" s="4">
+        <v>8379</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2537" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2537" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2537" s="4" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2538" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2538" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2538" s="4">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2539" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2539" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2539" s="4">
+        <v>8175</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2540" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2540" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2540" s="4">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2541" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2541" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2541" s="4">
+        <v>3788</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2542" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2542" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2542" s="4">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2543" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2543" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2543" s="4">
+        <v>9650</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2544" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2544" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2544" s="4">
+        <v>5632</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2545" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2545" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2545" s="4">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2546" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2546" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2546" s="4">
+        <v>6868</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2547" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2547" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2547" s="4">
+        <v>4885</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5916D7-E0C3-4743-B0A2-EFB3CE2FA9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA063157-F14E-4ED9-864D-3AD8CC715C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6048" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="1362">
   <si>
     <t>Name</t>
   </si>
@@ -4072,6 +4072,45 @@
   </si>
   <si>
     <t>0112</t>
+  </si>
+  <si>
+    <t>HARMEET GAWADI</t>
+  </si>
+  <si>
+    <t>UTIB0005387</t>
+  </si>
+  <si>
+    <t>GSCBOKTC013</t>
+  </si>
+  <si>
+    <t>BKID0003831</t>
+  </si>
+  <si>
+    <t>HDFC0CBMCBJ</t>
+  </si>
+  <si>
+    <t>CNRB0005316</t>
+  </si>
+  <si>
+    <t>0417</t>
+  </si>
+  <si>
+    <t>ICIC00USNDC</t>
+  </si>
+  <si>
+    <t>0040</t>
+  </si>
+  <si>
+    <t>0630</t>
+  </si>
+  <si>
+    <t>UBIN0918202</t>
+  </si>
+  <si>
+    <t>0331</t>
+  </si>
+  <si>
+    <t>IDIB000F518</t>
   </si>
 </sst>
 </file>
@@ -32396,6 +32435,402 @@
         <v>4885</v>
       </c>
     </row>
+    <row r="2548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2548" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B2548" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2548" s="4">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2549" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B2549" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2549" s="4">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2550" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B2550" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2550" s="4">
+        <v>5751</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2551" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2551" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2551" s="4">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2552" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B2552" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2552" s="4">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2553" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2553" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2553" s="4">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2554" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2554" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2554" s="4" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2555" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2555" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2555" s="4">
+        <v>8384</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2556" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2556" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2556" s="4">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2557" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2557" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2557" s="4">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2558" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2558" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2558" s="4">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2559" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2559" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2559" s="4">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2560" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2560" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2560" s="4">
+        <v>6541</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2561" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2561" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2561" s="4">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2562" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2562" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2562" s="4">
+        <v>8379</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2563" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2563" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C2563" s="4">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2564" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2564" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C2564" s="4">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2565" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2565" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C2565" s="4" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2566" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2566" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C2566" s="4">
+        <v>8679</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2567" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2567" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C2567" s="4" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2568" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2568" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2568" s="4">
+        <v>5471</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2569" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2569" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2569" s="4">
+        <v>5470</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2570" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2570" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C2570" s="4" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2571" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2571" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C2571" s="4" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2572" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2572" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2572" s="4" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2573" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2573" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C2573" s="4" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2574" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2574" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2574">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2575" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2575" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2575">
+        <v>8907</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2576" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2576" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2576">
+        <v>8882</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2577" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2577" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2577">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2578" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2578" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2578">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2579" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2579" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2579">
+        <v>6198</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2580" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2580" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2580">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2581" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2581" t="s">
+        <v>647</v>
+      </c>
+      <c r="C2581">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2582" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2582" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C2582">
+        <v>8085</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2583" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2583" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C2583">
+        <v>1425</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">
